--- a/version_1_photo_with_camera/vision_llm_output/receipts.xlsx
+++ b/version_1_photo_with_camera/vision_llm_output/receipts.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,7 +550,140 @@
           <t>THB</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-26T12:42:44</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Generated_invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-26T12:44:32</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Generated_invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-26T12:45:24</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Generated_invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-26T12:47:13</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Generated_invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-26T12:51:11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Generated_invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-26T12:56:26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Generated_invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-26T12:57:19</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Generated_invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-26T13:01:30</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Generated_invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-26T13:08:06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Generated_invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-26T13:57:04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Generated_invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-26T13:58:57</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Generated_invoice</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
